--- a/research/traditional_assets/database/data/denmark/denmark_environmental_waste_services.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_environmental_waste_services.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-1.065050505050505</v>
+        <v>-1.843950617283951</v>
       </c>
       <c r="H2">
-        <v>-1.111111111111111</v>
+        <v>-1.88641975308642</v>
       </c>
       <c r="I2">
-        <v>-1.363636363636364</v>
+        <v>-2.192592592592593</v>
       </c>
       <c r="J2">
-        <v>-1.363636363636364</v>
+        <v>-2.192592592592593</v>
       </c>
       <c r="K2">
-        <v>-8.68</v>
+        <v>-13.8</v>
       </c>
       <c r="L2">
-        <v>-1.753535353535354</v>
+        <v>-3.407407407407408</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,58 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.04</v>
+        <v>5.73</v>
       </c>
       <c r="V2">
-        <v>0.01496402877697842</v>
+        <v>0.2348360655737705</v>
+      </c>
+      <c r="W2">
+        <v>4.326018808777429</v>
       </c>
       <c r="X2">
-        <v>0.05770590956854075</v>
+        <v>0.107142986663394</v>
+      </c>
+      <c r="Y2">
+        <v>4.218875822114035</v>
+      </c>
+      <c r="Z2">
+        <v>0.3221957040572792</v>
+      </c>
+      <c r="AA2">
+        <v>-0.7064439140811456</v>
       </c>
       <c r="AB2">
-        <v>0.05118104725386311</v>
+        <v>0.09000122820272879</v>
+      </c>
+      <c r="AC2">
+        <v>-0.7964451422838744</v>
       </c>
       <c r="AD2">
-        <v>16.8</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>16.8</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AG2">
-        <v>15.76</v>
+        <v>3.15</v>
       </c>
       <c r="AH2">
-        <v>0.1946697566628042</v>
+        <v>0.2668269230769231</v>
       </c>
       <c r="AI2">
-        <v>1.234386480529023</v>
+        <v>0.4314868804664724</v>
       </c>
       <c r="AJ2">
-        <v>0.1848463523340371</v>
+        <v>0.1143375680580763</v>
       </c>
       <c r="AK2">
-        <v>1.253778838504375</v>
+        <v>0.2121212121212122</v>
       </c>
       <c r="AL2">
-        <v>1.65</v>
+        <v>2.26</v>
       </c>
       <c r="AM2">
-        <v>1.65</v>
+        <v>1.996</v>
       </c>
       <c r="AN2">
-        <v>-2.649842271293375</v>
+        <v>-1.037383177570093</v>
       </c>
       <c r="AO2">
-        <v>-4.090909090909091</v>
+        <v>-3.92920353982301</v>
       </c>
       <c r="AP2">
-        <v>-2.485804416403786</v>
+        <v>-0.3679906542056075</v>
       </c>
       <c r="AQ2">
-        <v>-4.090909090909091</v>
+        <v>-4.448897795591184</v>
       </c>
     </row>
     <row r="3">
@@ -698,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-1.065050505050505</v>
+        <v>-1.843950617283951</v>
       </c>
       <c r="H3">
-        <v>-1.111111111111111</v>
+        <v>-1.88641975308642</v>
       </c>
       <c r="I3">
-        <v>-1.363636363636364</v>
+        <v>-2.192592592592593</v>
       </c>
       <c r="J3">
-        <v>-1.363636363636364</v>
+        <v>-2.192592592592593</v>
       </c>
       <c r="K3">
-        <v>-8.68</v>
+        <v>-13.8</v>
       </c>
       <c r="L3">
-        <v>-1.753535353535354</v>
+        <v>-3.407407407407408</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -737,58 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.04</v>
+        <v>5.73</v>
       </c>
       <c r="V3">
-        <v>0.01496402877697842</v>
+        <v>0.2348360655737705</v>
+      </c>
+      <c r="W3">
+        <v>4.326018808777429</v>
       </c>
       <c r="X3">
-        <v>0.05770590956854075</v>
+        <v>0.107142986663394</v>
+      </c>
+      <c r="Y3">
+        <v>4.218875822114035</v>
+      </c>
+      <c r="Z3">
+        <v>0.3221957040572792</v>
+      </c>
+      <c r="AA3">
+        <v>-0.7064439140811456</v>
       </c>
       <c r="AB3">
-        <v>0.05118104725386311</v>
+        <v>0.09000122820272879</v>
+      </c>
+      <c r="AC3">
+        <v>-0.7964451422838744</v>
       </c>
       <c r="AD3">
-        <v>16.8</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>16.8</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AG3">
-        <v>15.76</v>
+        <v>3.15</v>
       </c>
       <c r="AH3">
-        <v>0.1946697566628042</v>
+        <v>0.2668269230769231</v>
       </c>
       <c r="AI3">
-        <v>1.234386480529023</v>
+        <v>0.4314868804664724</v>
       </c>
       <c r="AJ3">
-        <v>0.1848463523340371</v>
+        <v>0.1143375680580763</v>
       </c>
       <c r="AK3">
-        <v>1.253778838504375</v>
+        <v>0.2121212121212122</v>
       </c>
       <c r="AL3">
-        <v>1.65</v>
+        <v>2.26</v>
       </c>
       <c r="AM3">
-        <v>1.65</v>
+        <v>1.996</v>
       </c>
       <c r="AN3">
-        <v>-2.649842271293375</v>
+        <v>-1.037383177570093</v>
       </c>
       <c r="AO3">
-        <v>-4.090909090909091</v>
+        <v>-3.92920353982301</v>
       </c>
       <c r="AP3">
-        <v>-2.485804416403786</v>
+        <v>-0.3679906542056075</v>
       </c>
       <c r="AQ3">
-        <v>-4.090909090909091</v>
+        <v>-4.448897795591184</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/denmark/denmark_environmental_waste_services.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_environmental_waste_services.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-1.843950617283951</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>-1.88641975308642</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>-2.192592592592593</v>
+        <v>-44.74576271186441</v>
       </c>
       <c r="J2">
-        <v>-2.192592592592593</v>
+        <v>-44.74576271186441</v>
       </c>
       <c r="K2">
-        <v>-13.8</v>
+        <v>-4.33</v>
       </c>
       <c r="L2">
-        <v>-3.407407407407408</v>
+        <v>-73.38983050847457</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +627,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>5.73</v>
+        <v>4.71</v>
       </c>
       <c r="V2">
-        <v>0.2348360655737705</v>
+        <v>0.0256396298312466</v>
       </c>
       <c r="W2">
-        <v>4.326018808777429</v>
+        <v>-0.6797488226059655</v>
       </c>
       <c r="X2">
-        <v>0.107142986663394</v>
+        <v>0.07860742356159683</v>
       </c>
       <c r="Y2">
-        <v>4.218875822114035</v>
+        <v>-0.7583562461675624</v>
       </c>
       <c r="Z2">
-        <v>0.3221957040572792</v>
+        <v>0.005253784505788068</v>
       </c>
       <c r="AA2">
-        <v>-0.7064439140811456</v>
+        <v>-0.2350845948352627</v>
       </c>
       <c r="AB2">
-        <v>0.09000122820272879</v>
+        <v>0.07533475097353838</v>
       </c>
       <c r="AC2">
-        <v>-0.7964451422838744</v>
+        <v>-0.3104193458088011</v>
       </c>
       <c r="AD2">
-        <v>8.880000000000001</v>
+        <v>17.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>8.880000000000001</v>
+        <v>17.9</v>
       </c>
       <c r="AG2">
-        <v>3.15</v>
+        <v>13.19</v>
       </c>
       <c r="AH2">
-        <v>0.2668269230769231</v>
+        <v>0.08878968253968253</v>
       </c>
       <c r="AI2">
-        <v>0.4314868804664724</v>
+        <v>0.8016121809225257</v>
       </c>
       <c r="AJ2">
-        <v>0.1143375680580763</v>
+        <v>0.06699172126568134</v>
       </c>
       <c r="AK2">
-        <v>0.2121212121212122</v>
+        <v>0.7485811577752554</v>
       </c>
       <c r="AL2">
-        <v>2.26</v>
+        <v>1.36</v>
       </c>
       <c r="AM2">
-        <v>1.996</v>
-      </c>
-      <c r="AN2">
-        <v>-1.037383177570093</v>
+        <v>1.353</v>
       </c>
       <c r="AO2">
-        <v>-3.92920353982301</v>
-      </c>
-      <c r="AP2">
-        <v>-0.3679906542056075</v>
+        <v>-1.941176470588235</v>
       </c>
       <c r="AQ2">
-        <v>-4.448897795591184</v>
+        <v>-1.951219512195122</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +698,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Re-Match Holding A/S (CPSE:RMATCH)</t>
+          <t>WPU - Waste Plastic Upcycling A/S (OB:WPU)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,22 +707,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-1.843950617283951</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>-1.88641975308642</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>-2.192592592592593</v>
+        <v>-44.74576271186441</v>
       </c>
       <c r="J3">
-        <v>-2.192592592592593</v>
+        <v>-44.74576271186441</v>
       </c>
       <c r="K3">
-        <v>-13.8</v>
+        <v>-4.33</v>
       </c>
       <c r="L3">
-        <v>-3.407407407407408</v>
+        <v>-73.38983050847457</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +746,67 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>5.73</v>
+        <v>4.71</v>
       </c>
       <c r="V3">
-        <v>0.2348360655737705</v>
+        <v>0.0256396298312466</v>
       </c>
       <c r="W3">
-        <v>4.326018808777429</v>
+        <v>-0.6797488226059655</v>
       </c>
       <c r="X3">
-        <v>0.107142986663394</v>
+        <v>0.07860742356159683</v>
       </c>
       <c r="Y3">
-        <v>4.218875822114035</v>
+        <v>-0.7583562461675624</v>
       </c>
       <c r="Z3">
-        <v>0.3221957040572792</v>
+        <v>0.005253784505788068</v>
       </c>
       <c r="AA3">
-        <v>-0.7064439140811456</v>
+        <v>-0.2350845948352627</v>
       </c>
       <c r="AB3">
-        <v>0.09000122820272879</v>
+        <v>0.07533475097353838</v>
       </c>
       <c r="AC3">
-        <v>-0.7964451422838744</v>
+        <v>-0.3104193458088011</v>
       </c>
       <c r="AD3">
-        <v>8.880000000000001</v>
+        <v>17.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>8.880000000000001</v>
+        <v>17.9</v>
       </c>
       <c r="AG3">
-        <v>3.15</v>
+        <v>13.19</v>
       </c>
       <c r="AH3">
-        <v>0.2668269230769231</v>
+        <v>0.08878968253968253</v>
       </c>
       <c r="AI3">
-        <v>0.4314868804664724</v>
+        <v>0.8016121809225257</v>
       </c>
       <c r="AJ3">
-        <v>0.1143375680580763</v>
+        <v>0.06699172126568134</v>
       </c>
       <c r="AK3">
-        <v>0.2121212121212122</v>
+        <v>0.7485811577752554</v>
       </c>
       <c r="AL3">
-        <v>2.26</v>
+        <v>1.36</v>
       </c>
       <c r="AM3">
-        <v>1.996</v>
-      </c>
-      <c r="AN3">
-        <v>-1.037383177570093</v>
+        <v>1.353</v>
       </c>
       <c r="AO3">
-        <v>-3.92920353982301</v>
-      </c>
-      <c r="AP3">
-        <v>-0.3679906542056075</v>
+        <v>-1.941176470588235</v>
       </c>
       <c r="AQ3">
-        <v>-4.448897795591184</v>
+        <v>-1.951219512195122</v>
       </c>
     </row>
   </sheetData>
